--- a/plantillas_117_integradas_v7/Plantilla_Excel_Bloque_23_IN_Piura.xlsx
+++ b/plantillas_117_integradas_v7/Plantilla_Excel_Bloque_23_IN_Piura.xlsx
@@ -573,7 +573,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Gráficos de integración'!B29</f>
+              <f>'Gráficos de integración'!B27</f>
             </strRef>
           </tx>
           <spPr>
@@ -583,12 +583,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Gráficos de integración'!$A$30:$A$34</f>
+              <f>'Gráficos de integración'!$A$28:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gráficos de integración'!$B$30:$B$34</f>
+              <f>'Gráficos de integración'!$B$28:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -668,7 +668,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Gráficos de integración'!B52</f>
+              <f>'Gráficos de integración'!B46</f>
             </strRef>
           </tx>
           <spPr>
@@ -678,12 +678,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Gráficos de integración'!$A$53</f>
+              <f>'Gráficos de integración'!$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gráficos de integración'!$B$53</f>
+              <f>'Gráficos de integración'!$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -761,7 +761,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Gráficos de integración'!B71</f>
+              <f>'Gráficos de integración'!B65</f>
             </strRef>
           </tx>
           <spPr>
@@ -771,12 +771,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Gráficos de integración'!$A$72:$A$75</f>
+              <f>'Gráficos de integración'!$A$66:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gráficos de integración'!$B$72:$B$75</f>
+              <f>'Gráficos de integración'!$B$66:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -820,7 +820,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
@@ -842,7 +842,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
@@ -864,7 +864,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2880000"/>
@@ -3629,7 +3629,7 @@
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
-          <t>Cruce de la ficha de campo F-DT vigente con la ficha de resumen de gabinete y el catálogo maestro. Integración 2026-09-11 20:22:26.</t>
+          <t>Cruce de la ficha de campo F-DT vigente con la ficha de resumen de gabinete y el catálogo maestro. Integración 2026-09-11 21:26:24.</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5494,160 +5494,160 @@
         <v>14</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>Estado del cruce entre fuentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t>Hechos</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="54" t="inlineStr">
-        <is>
-          <t>Estado del cruce entre fuentes</t>
-        </is>
+      <c r="A28" s="56" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="B28" s="56" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="55" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B29" s="55" t="inlineStr">
-        <is>
-          <t>Hechos</t>
-        </is>
+      <c r="A29" s="57" t="inlineStr">
+        <is>
+          <t>COMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="B29" s="57" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="56" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="B30" s="56" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="57" t="inlineStr">
         <is>
-          <t>COMPLEMENTADO</t>
+          <t>DISCREPANTE</t>
         </is>
       </c>
       <c r="B31" s="57" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="56" t="inlineStr">
         <is>
-          <t>ACTUALIZADO</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="B32" s="56" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="54" t="inlineStr">
+        <is>
+          <t>Cobertura por estrato — campo (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="55" t="inlineStr">
+        <is>
+          <t>Estrato</t>
+        </is>
+      </c>
+      <c r="B46" s="55" t="inlineStr">
+        <is>
+          <t>% del área</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="56" t="inlineStr">
+        <is>
+          <t>Suelo desnudo</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="54" t="inlineStr">
+        <is>
+          <t>Control de consistencia por calificación</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="55" t="inlineStr">
+        <is>
+          <t>Calificación</t>
+        </is>
+      </c>
+      <c r="B65" s="55" t="inlineStr">
+        <is>
+          <t>Verificaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="56" t="inlineStr">
+        <is>
+          <t>SUSTANTIVA</t>
+        </is>
+      </c>
+      <c r="B66" s="56" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="57" t="inlineStr">
+        <is>
+          <t>NO SUSTANTIVA</t>
+        </is>
+      </c>
+      <c r="B67" s="57" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="56" t="inlineStr">
+        <is>
+          <t>CORREGIDO</t>
+        </is>
+      </c>
+      <c r="B68" s="56" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="57" t="inlineStr">
-        <is>
-          <t>DISCREPANTE</t>
-        </is>
-      </c>
-      <c r="B33" s="57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="56" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="B34" s="56" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="54" t="inlineStr">
-        <is>
-          <t>Cobertura por estrato — campo (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="55" t="inlineStr">
-        <is>
-          <t>Estrato</t>
-        </is>
-      </c>
-      <c r="B52" s="55" t="inlineStr">
-        <is>
-          <t>% del área</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="56" t="inlineStr">
-        <is>
-          <t>Suelo desnudo</t>
-        </is>
-      </c>
-      <c r="B53" s="61" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="54" t="inlineStr">
-        <is>
-          <t>Control de consistencia por calificación</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="55" t="inlineStr">
-        <is>
-          <t>Calificación</t>
-        </is>
-      </c>
-      <c r="B71" s="55" t="inlineStr">
-        <is>
-          <t>Verificaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="56" t="inlineStr">
-        <is>
-          <t>SUSTANTIVA</t>
-        </is>
-      </c>
-      <c r="B72" s="56" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="57" t="inlineStr">
-        <is>
-          <t>NO SUSTANTIVA</t>
-        </is>
-      </c>
-      <c r="B73" s="57" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="56" t="inlineStr">
-        <is>
-          <t>CORREGIDO</t>
-        </is>
-      </c>
-      <c r="B74" s="56" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="57" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="57" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="B75" s="57" t="n">
+      <c r="B69" s="57" t="n">
         <v>9</v>
       </c>
     </row>
